--- a/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/ledger-batch-preview.xlsx
+++ b/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/ledger-batch-preview.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="10">
+  <x:numFmts count="14">
     <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -20,6 +20,10 @@
     <x:numFmt numFmtId="179" formatCode="0.000"/>
     <x:numFmt numFmtId="200" formatCode="mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
+    <x:numFmt numFmtId="210" formatCode="0"/>
+    <x:numFmt numFmtId="211" formatCode="0.0"/>
+    <x:numFmt numFmtId="212" formatCode="0.00"/>
+    <x:numFmt numFmtId="213" formatCode="0.000"/>
   </x:numFmts>
   <x:fonts count="26">
     <x:font>
@@ -614,7 +618,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="80">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -834,17 +838,26 @@
     <x:xf numFmtId="201" fontId="25" fillId="41" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1262,6 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.372726440429688" style="1" customWidth="1"/>
@@ -1275,36 +1289,36 @@
     <row r="1" ht="21.95" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">日期</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">支出明细</t>
+          <t>支出明细</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">支出金额</t>
+          <t>支出金额</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">合计</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">支出人</t>
+          <t>支出人</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="21.95" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="73"/>
       <c r="B2" s="74"/>
       <c r="C2" s="75"/>
@@ -1313,5 +1327,6 @@
       <c r="F2" s="74"/>
     </row>
   </sheetData>
+  <mergeCells count="0"/>
 </worksheet>
 </file>